--- a/report-2026-06-30.xlsx
+++ b/report-2026-06-30.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-30T07:09:19+05:30</t>
+    <t>Generated 2026-06-30T07:09:21+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-29T10:10:40+05:30 (20h58m39s ago)</t>
+    <t>2026-06-29T10:10:40+05:30 (20h58m41s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -489,7 +489,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-30T07:09:19+05:30</t>
+    <t>2026-06-30T07:09:21+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>21h 14m 37s</t>
+          <t>21h 14m 41s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>07:09:18</t>
+          <t>07:09:21</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>07:09:18</t>
+          <t>07:09:21</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>07:09:18</t>
+          <t>07:09:21</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>07:09:18</t>
+          <t>07:09:21</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-30.xlsx
+++ b/report-2026-06-30.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-30T07:09:21+05:30</t>
+    <t>Generated 2026-06-30T07:09:23+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-29T10:10:40+05:30 (20h58m41s ago)</t>
+    <t>2026-06-29T10:10:40+05:30 (20h58m43s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -489,7 +489,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-30T07:09:21+05:30</t>
+    <t>2026-06-30T07:09:23+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>21h 14m 41s</t>
+          <t>21h 14m 43s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>07:09:21</t>
+          <t>07:09:23</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>07:09:21</t>
+          <t>07:09:23</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>07:09:21</t>
+          <t>07:09:23</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>07:09:21</t>
+          <t>07:09:23</t>
         </is>
       </c>
     </row>

--- a/report-2026-06-30.xlsx
+++ b/report-2026-06-30.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-30T07:09:23+05:30</t>
+    <t>Generated 2026-06-30T07:09:26+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-29T10:10:40+05:30 (20h58m43s ago)</t>
+    <t>2026-06-29T10:10:40+05:30 (20h58m45s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -489,7 +489,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-30T07:09:23+05:30</t>
+    <t>2026-06-30T07:09:26+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>21h 14m 43s</t>
+          <t>21h 14m 46s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>87h 56m 44s</t>
+          <t>87h 56m 49s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>07:09:23</t>
+          <t>07:09:26</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>07:09:23</t>
+          <t>07:09:26</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>07:09:23</t>
+          <t>07:09:26</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>07:09:23</t>
+          <t>07:09:26</t>
         </is>
       </c>
     </row>
